--- a/public/descargas/test-de-madurez-operativa-2026.xlsx
+++ b/public/descargas/test-de-madurez-operativa-2026.xlsx
@@ -2095,8 +2095,8 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="9" t="str">
-        <f aca="false">HYPERLINK("https://www.procesosclaros.cl/contacto","¿Prefieres revisarlo conmigo? Agenda el diagnóstico gratuito de 30 minutos →")</f>
-        <v>¿Prefieres revisarlo conmigo? Agenda el diagnóstico gratuito de 30 minutos →</v>
+        <f aca="false">HYPERLINK("mailto:jorge@procesosclaros.cl?subject=Resultado%20del%20test%20de%20madurez","¿Quieres revisarlo conmigo? Envíame este archivo completado a jorge@procesosclaros.cl →")</f>
+        <v>¿Quieres revisarlo conmigo? Envíame este archivo completado a jorge@procesosclaros.cl →</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
